--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יערה טופ – Kill Me</v>
+        <v>Garden City Movement – I Can Be Your Salvation</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%a2%d7%a8%d7%94-%d7%98%d7%95%d7%a4-kill-me/</v>
+        <v>https://yosmusic.com/garden-city-movement/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>יערה טופ שרה בלדת פולק אקוסטית עדינה, כמעט חשופה, שמצליחה להחזיק בתוכה טקסט טעון  על תשוקה, תלות, ופחד מאינטימיות. למרות הכותרת הדרמטית, זה אינו שיר על מוות כפשוטו, אלא על הסכמה להיעלם בתוך אהבה ועל הסכנה שבכך. ה”Kill me” היא</v>
+        <v>בלב המוזיקה האוורירית-אלקטרונית של הצמד יוני שרוני  ורועי אביטל המהווים  את Garden City Movement מסתתר טקסט לא רגוע בכלל. זוהי מוסיקה ריחופית שמדברת על שליטה, בלבול ותלות רגשית בעידן של עודף גירויים. השורה הראשונה מציבה את הדילמה: “?Could you choose</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,50 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יערה טופ – Kill Me</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>אלדד ציטרין וגלי עטרי – רק במנגינה</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-02-22</v>
-      </c>
-      <c r="C3" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%9c%d7%93%d7%93-%d7%a6%d7%99%d7%98%d7%a8%d7%99%d7%9f-%d7%95%d7%92%d7%9c%d7%99-%d7%a2%d7%98%d7%a8%d7%99-%d7%a8%d7%a7-%d7%91%d7%9e%d7%a0%d7%92%d7%99%d7%a0%d7%94/</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-02-22</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v>זהו שיר שקט, מינימליסטי, מעודן, תואם את גוון שירתה של גלי עטרי. בתוכו מתקיים דיאלוג על ערך עצמי אחרי פרידה. לא מדובר בשיר אהבה, אלא בשיר על תיקון חלקי. הוא נפתח בשאלות: “מי לך אמר את לא מיוחדת מי לך</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>אלדד ציטרין וגלי עטרי – רק במנגינה</v>
+        <v>Garden City Movement – I Can Be Your Salvation</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Garden City Movement – I Can Be Your Salvation</v>
+        <v>מירי מסיקה – גידי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-23</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/garden-city-movement/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%99%d7%a8%d7%99-%d7%9e%d7%a1%d7%99%d7%a7%d7%94-%d7%92%d7%99%d7%93%d7%99/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-23</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>בלב המוזיקה האוורירית-אלקטרונית של הצמד יוני שרוני  ורועי אביטל המהווים  את Garden City Movement מסתתר טקסט לא רגוע בכלל. זוהי מוסיקה ריחופית שמדברת על שליטה, בלבול ותלות רגשית בעידן של עודף גירויים. השורה הראשונה מציבה את הדילמה: “?Could you choose</v>
+        <v>"גידי” הוא שיר פופ דרמטי של שרון ליפשיץ משנות ה־80 שמגלם נשיות תיאטרלית, הנמצאת בסיטואציה של אהבה תלויה.החידוש של מירי מסיקה (במסגרת הסדרה "ריסט") לוקח את אותו טקסט טעון  ומלביש עליו אסתטיקה אלקטרונית עדכנית עם גרוב פאנקי ובס מודגש, מה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Garden City Movement – I Can Be Your Salvation</v>
+        <v>מירי מסיקה – גידי</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מירי מסיקה – גידי</v>
+        <v>בר צברי – ראש לאריות</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-23</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%99%d7%a8%d7%99-%d7%9e%d7%a1%d7%99%d7%a7%d7%94-%d7%92%d7%99%d7%93%d7%99/</v>
+        <v>https://yosmusic.com/%d7%91%d7%a8-%d7%a6%d7%91%d7%a8%d7%99-%d7%a8%d7%90%d7%a9-%d7%9c%d7%90%d7%a8%d7%99%d7%95%d7%aa/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-23</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"גידי” הוא שיר פופ דרמטי של שרון ליפשיץ משנות ה־80 שמגלם נשיות תיאטרלית, הנמצאת בסיטואציה של אהבה תלויה.החידוש של מירי מסיקה (במסגרת הסדרה "ריסט") לוקח את אותו טקסט טעון  ומלביש עליו אסתטיקה אלקטרונית עדכנית עם גרוב פאנקי ובס מודגש, מה</v>
+        <v>השיר "ראש לאריות" של בר צברי נכתב לזכרו של לוחם הימ״מ ארנון זמורה ז״ל, שנהרג במבצע חילוץ בעזה במהלך מלחמת חרבות ברזל. זוהי בלדה אישית ואינטימית שהופכת מדמות פרטית – אדם, אב ובעל – לסמל של גבורה ישראלית. כבר מן</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מירי מסיקה – גידי</v>
+        <v>בר צברי – ראש לאריות</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>בר צברי – ראש לאריות</v>
+        <v>הפרויקט של תמרי ואהוד בנאי – יוצא לאור</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-23</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%a8-%d7%a6%d7%91%d7%a8%d7%99-%d7%a8%d7%90%d7%a9-%d7%9c%d7%90%d7%a8%d7%99%d7%95%d7%aa/</v>
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%aa%d7%9e%d7%a8%d7%99-%d7%95%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%99%d7%95%d7%a6%d7%90-%d7%9c%d7%90%d7%95%d7%a8/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-23</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "ראש לאריות" של בר צברי נכתב לזכרו של לוחם הימ״מ ארנון זמורה ז״ל, שנהרג במבצע חילוץ בעזה במהלך מלחמת חרבות ברזל. זוהי בלדה אישית ואינטימית שהופכת מדמות פרטית – אדם, אב ובעל – לסמל של גבורה ישראלית. כבר מן</v>
+        <v>חוזרים לשביל של אהוד בנאי עם "הפרויקט של תמרי" בשיתוף היוצר. השביל הזה מתחיל מכאן, כלומר – מהמקום בו אתה עומד – מתחיל שביל שמוליך אל דבר לא ברור, אל אותו דבר שאתה רוצה לעשות, אבל אתה לא יודע איך"…</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,50 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>בר צברי – ראש לאריות</v>
+        <v>הפרויקט של תמרי ואהוד בנאי – יוצא לאור</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>אייל אבן צור – פסל</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-02-23</v>
+      </c>
+      <c r="C3" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%99%d7%99%d7%9c-%d7%90%d7%91%d7%9f-%d7%a6%d7%95%d7%a8-%d7%a4%d7%a1%d7%9c/</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-02-23</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>השיר "פסל" של אייל אבן צור הוא יצירה אינטימית ועדינה, שנשענת על עיבוד פופ־פולק מלודי בעל אווירה מלנכולית מאופקת. הביצוע בטון גבוה ומתכוון יוצר תחושת פגיעות – קול שנשמע כבוי במידה מסוימת, אך לא נשבר. יש בו המשכיות מתכוונת, כמו</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>אייל אבן צור – פסל</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>הפרויקט של תמרי ואהוד בנאי – יוצא לאור</v>
+        <v>טוהר קדוש – סוף פואטי</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%aa%d7%9e%d7%a8%d7%99-%d7%95%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%99%d7%95%d7%a6%d7%90-%d7%9c%d7%90%d7%95%d7%a8/</v>
+        <v>https://yosmusic.com/%d7%98%d7%95%d7%94%d7%a8-%d7%a7%d7%93%d7%95%d7%a9-%d7%a1%d7%95%d7%a3-%d7%a4%d7%95%d7%90%d7%98%d7%99/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>חוזרים לשביל של אהוד בנאי עם "הפרויקט של תמרי" בשיתוף היוצר. השביל הזה מתחיל מכאן, כלומר – מהמקום בו אתה עומד – מתחיל שביל שמוליך אל דבר לא ברור, אל אותו דבר שאתה רוצה לעשות, אבל אתה לא יודע איך"…</v>
+        <v>השיר "סוף פואטי" של טוהר קדוש הוא בלדה אפלה על אחיזה נואשת באהבה שכבר איננה  דרך טקסים, פנטזיות ופולחן רגשי. העיבוד האלקטרוני העדין, בקצב מיד־טמפו איטי, יוצר תחושת לופ מתמשך גם מוזיקלית וגם נפשית. זו לא דרמה מתפרצת, אלא שחיקה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,50 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>הפרויקט של תמרי ואהוד בנאי – יוצא לאור</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>אייל אבן צור – פסל</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="C3" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%99%d7%99%d7%9c-%d7%90%d7%91%d7%9f-%d7%a6%d7%95%d7%a8-%d7%a4%d7%a1%d7%9c/</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v>השיר "פסל" של אייל אבן צור הוא יצירה אינטימית ועדינה, שנשענת על עיבוד פופ־פולק מלודי בעל אווירה מלנכולית מאופקת. הביצוע בטון גבוה ומתכוון יוצר תחושת פגיעות – קול שנשמע כבוי במידה מסוימת, אך לא נשבר. יש בו המשכיות מתכוונת, כמו</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>אייל אבן צור – פסל</v>
+        <v>טוהר קדוש – סוף פואטי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>טוהר קדוש – סוף פואטי</v>
+        <v>נדב דלומי – מאיר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-24</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%98%d7%95%d7%94%d7%a8-%d7%a7%d7%93%d7%95%d7%a9-%d7%a1%d7%95%d7%a3-%d7%a4%d7%95%d7%90%d7%98%d7%99/</v>
+        <v>https://yosmusic.com/%d7%a0%d7%93%d7%91-%d7%93%d7%9c%d7%95%d7%9e%d7%99-%d7%9e%d7%90%d7%99%d7%a8/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-24</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "סוף פואטי" של טוהר קדוש הוא בלדה אפלה על אחיזה נואשת באהבה שכבר איננה  דרך טקסים, פנטזיות ופולחן רגשי. העיבוד האלקטרוני העדין, בקצב מיד־טמפו איטי, יוצר תחושת לופ מתמשך גם מוזיקלית וגם נפשית. זו לא דרמה מתפרצת, אלא שחיקה</v>
+        <v>השיר “מאיר” של נדב דלומי הוא שיר צער אישי הנע בין הבטחה לגאולה לבין התפכחות כואבת. זהו מסע כפול – גיאוגרפי ונפשי – מן הבית בעיראק אל ישראל, מן הענן המרחף אל אדמת הטרשים, מן השמש והירח כסמלי אור אל</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>טוהר קדוש – סוף פואטי</v>
+        <v>נדב דלומי – מאיר</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week04/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נדב דלומי – מאיר</v>
+        <v>הראל ליסמן – אל תדאג</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%93%d7%91-%d7%93%d7%9c%d7%95%d7%9e%d7%99-%d7%9e%d7%90%d7%99%d7%a8/</v>
+        <v>https://yosmusic.com/%d7%94%d7%a8%d7%90%d7%9c-%d7%9c%d7%99%d7%a1%d7%9e%d7%9f-%d7%90%d7%9c-%d7%aa%d7%93%d7%90%d7%92/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר “מאיר” של נדב דלומי הוא שיר צער אישי הנע בין הבטחה לגאולה לבין התפכחות כואבת. זהו מסע כפול – גיאוגרפי ונפשי – מן הבית בעיראק אל ישראל, מן הענן המרחף אל אדמת הטרשים, מן השמש והירח כסמלי אור אל</v>
+        <v>“אל תדאג” היא בלדת פופ אמוציונלית הבנויה כווידוי פנימי שמופנה החוצה,  אך למעשה מדבר פנימה. זהו שיר שנכתב מתוך עייפות שקטה: לא קריסה דרמטית, אלא שחיקה מתמשכת של מי שמורגל לבקש אישור, להחזיק תדמית יציבה וחזקה, ובתוך כך לנהל מאבק</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נדב דלומי – מאיר</v>
+        <v>הראל ליסמן – אל תדאג</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>הראל ליסמן – אל תדאג</v>
+        <v>גיא יהוד – חיבוק אחרון</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-25</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%a8%d7%90%d7%9c-%d7%9c%d7%99%d7%a1%d7%9e%d7%9f-%d7%90%d7%9c-%d7%aa%d7%93%d7%90%d7%92/</v>
+        <v>https://yosmusic.com/%d7%92%d7%99%d7%90-%d7%99%d7%94%d7%95%d7%93-%d7%97%d7%99%d7%91%d7%95%d7%a7-%d7%90%d7%97%d7%a8%d7%95%d7%9f/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-25</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>“אל תדאג” היא בלדת פופ אמוציונלית הבנויה כווידוי פנימי שמופנה החוצה,  אך למעשה מדבר פנימה. זהו שיר שנכתב מתוך עייפות שקטה: לא קריסה דרמטית, אלא שחיקה מתמשכת של מי שמורגל לבקש אישור, להחזיק תדמית יציבה וחזקה, ובתוך כך לנהל מאבק</v>
+        <v>“חיבוק אחרון” מבוצע בתפקיד כפול – גיא יהוד מגלם גם את קולה של הדוברת הנשברת וגם את קולו של בן הזוג המנסה להרגיע, להסביר או להיאחז. הבחירה הזו מייצרת דרמה פנימית, כמעט דיאלוג תיאטרלי בתוך שיר פופ ים־תיכוני. השיר נשען</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>הראל ליסמן – אל תדאג</v>
+        <v>גיא יהוד – חיבוק אחרון</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week04/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>גיא יהוד – חיבוק אחרון</v>
+        <v>אמיר דדון – רחובות ריקים</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%92%d7%99%d7%90-%d7%99%d7%94%d7%95%d7%93-%d7%97%d7%99%d7%91%d7%95%d7%a7-%d7%90%d7%97%d7%a8%d7%95%d7%9f/</v>
+        <v>https://yosmusic.com/%d7%90%d7%9e%d7%99%d7%a8-%d7%93%d7%93%d7%95%d7%9f-%d7%a8%d7%97%d7%95%d7%91%d7%95%d7%aa-%d7%a8%d7%99%d7%a7%d7%99%d7%9d/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-26</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>“חיבוק אחרון” מבוצע בתפקיד כפול – גיא יהוד מגלם גם את קולה של הדוברת הנשברת וגם את קולו של בן הזוג המנסה להרגיע, להסביר או להיאחז. הבחירה הזו מייצרת דרמה פנימית, כמעט דיאלוג תיאטרלי בתוך שיר פופ ים־תיכוני. השיר נשען</v>
+        <v>אמיר דדון בנה לעצמו לאורך השנים זהות של זמר-מספר: קול עמוק, מחוספס אך נקי, שמחזיק שירים פשוטים ומטעין אותם במשקל רגשי כבד. “רחובות ריקים” הוא דוגמה מובהקת לאופן שבו בלדת אהבה לכאורה מינימלית הופכת בידיים הנכונות לאמירה עוצמתית וכנה. השיר</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>גיא יהוד – חיבוק אחרון</v>
+        <v>אמיר דדון – רחובות ריקים</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אמיר דדון – רחובות ריקים</v>
+        <v>שרון הולצמן – מחמיץ</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-26</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%9e%d7%99%d7%a8-%d7%93%d7%93%d7%95%d7%9f-%d7%a8%d7%97%d7%95%d7%91%d7%95%d7%aa-%d7%a8%d7%99%d7%a7%d7%99%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%a8%d7%95%d7%9f-%d7%94%d7%95%d7%9c%d7%a6%d7%9e%d7%9f-%d7%9e%d7%97%d7%9e%d7%99%d7%a5/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-26</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>אמיר דדון בנה לעצמו לאורך השנים זהות של זמר-מספר: קול עמוק, מחוספס אך נקי, שמחזיק שירים פשוטים ומטעין אותם במשקל רגשי כבד. “רחובות ריקים” הוא דוגמה מובהקת לאופן שבו בלדת אהבה לכאורה מינימלית הופכת בידיים הנכונות לאמירה עוצמתית וכנה. השיר</v>
+        <v>“מחמיץ” ששר שרון הולצמן בזחיחות דעת, הוא שיר שנשמע תחילה כמו בדיחה קטנה על קנאה חברתית,  אבל בהאזנה עמוקה מתגלה כטקסט ציני, חתרני ואפילו פוליטי במסווה של הומור יבש. הוא מתבסס על פעלול הכפילות הלשונית: להחמיץ = לפספס, להחמיץ =</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אמיר דדון – רחובות ריקים</v>
+        <v>שרון הולצמן – מחמיץ</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week04/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שרון הולצמן – מחמיץ</v>
+        <v>Romi – תביטי בך</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%a8%d7%95%d7%9f-%d7%94%d7%95%d7%9c%d7%a6%d7%9e%d7%9f-%d7%9e%d7%97%d7%9e%d7%99%d7%a5/</v>
+        <v>https://yosmusic.com/romi-%d7%aa%d7%91%d7%99%d7%98%d7%99-%d7%91%d7%9a/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-26</v>
+        <v>2026-02-28</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>“מחמיץ” ששר שרון הולצמן בזחיחות דעת, הוא שיר שנשמע תחילה כמו בדיחה קטנה על קנאה חברתית,  אבל בהאזנה עמוקה מתגלה כטקסט ציני, חתרני ואפילו פוליטי במסווה של הומור יבש. הוא מתבסס על פעלול הכפילות הלשונית: להחמיץ = לפספס, להחמיץ =</v>
+        <v>“תביטי בך” של רומי אטון הוא שיר של מהלך מוזיקלי ורגשי מעניין : הוא מתחיל כהתכנסות פנימית כמעט מדיטטיבית, ואז מחליף שני הילוכים לפזמון בתנועת סמבה-סווינג מפתיעה, כמעט מנוגדת למה שנאמר במילים. הבתים בנויים סביב תחושת עומס מודרני: “למצוא אותי</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שרון הולצמן – מחמיץ</v>
+        <v>Romi – תביטי בך</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Romi – תביטי בך</v>
+        <v>בן שוקרון – נותן לזה ללכת</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-27</v>
+        <v>2026-02-28</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/romi-%d7%aa%d7%91%d7%99%d7%98%d7%99-%d7%91%d7%9a/</v>
+        <v>https://yosmusic.com/%d7%91%d7%9f-%d7%a9%d7%95%d7%a7%d7%a8%d7%95%d7%9f-%d7%a0%d7%95%d7%aa%d7%9f-%d7%9c%d7%96%d7%94-%d7%9c%d7%9c%d7%9b%d7%aa/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-28</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>“תביטי בך” של רומי אטון הוא שיר של מהלך מוזיקלי ורגשי מעניין : הוא מתחיל כהתכנסות פנימית כמעט מדיטטיבית, ואז מחליף שני הילוכים לפזמון בתנועת סמבה-סווינג מפתיעה, כמעט מנוגדת למה שנאמר במילים. הבתים בנויים סביב תחושת עומס מודרני: “למצוא אותי</v>
+        <v>זהו שיר שממוקם בבירור בתוך גל היצירה הישראלי שאחרי השבעה באוקטובר לא כשיר זיכרון לאומי ישיר, אלא כעדות פנימית, כמעט טיפולית, של אדם המתמודד עם פוסט־טראומה. בניגוד לשירי אבל דרמטיים, כאן הבחירה של בן שוקרון היא בתהליך של שיקום איטי.</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Romi – תביטי בך</v>
+        <v>בן שוקרון – נותן לזה ללכת</v>
       </c>
     </row>
   </sheetData>
